--- a/teachergr.xlsx
+++ b/teachergr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\2025.11.26.부터\2026\성과상여금\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDD259E-1767-474F-B551-486EE50DE232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4CD83B-85E5-4228-AAD2-B23937105C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{2E82CF06-4291-4BB2-932B-E63723969F27}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E82CF06-4291-4BB2-932B-E63723969F27}"/>
   </bookViews>
   <sheets>
     <sheet name="최종명단" sheetId="2" r:id="rId1"/>
@@ -1197,7 +1197,7 @@
         <v>47</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -1208,7 +1208,7 @@
         <v>48</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
